--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -79,28 +79,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>MATLATECATL</t>
   </si>
   <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
   </si>
   <si>
     <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
   </si>
 </sst>
 </file>
@@ -950,7 +986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,22 +1018,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920260</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1005,22 +1041,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920234</v>
+        <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1028,16 +1064,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920240</v>
+        <v>21330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1047,6 +1083,98 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920240</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920036</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920037</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920260</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -79,64 +79,85 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>COBOS</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>NAZARIO</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>YOLET</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
   </si>
   <si>
     <t>EDGAR</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
   </si>
 </sst>
 </file>
@@ -560,7 +581,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -569,10 +590,10 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -706,16 +727,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.18000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -726,19 +750,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -752,16 +779,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -863,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -883,22 +913,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>28</v>
       </c>
       <c r="G3">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -915,16 +945,16 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>89.47</v>
+        <v>81.58</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -986,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1018,22 +1048,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1041,22 +1071,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920018</v>
+        <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1064,22 +1094,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920234</v>
+        <v>21330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1087,16 +1117,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920240</v>
+        <v>21330051920234</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1110,22 +1140,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920036</v>
+        <v>21330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1133,22 +1163,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920037</v>
+        <v>21330051920240</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1156,24 +1186,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920260</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920037</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920018</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -88,9 +88,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>MENA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
   </si>
   <si>
     <t>ANGELES</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
@@ -1016,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,10 +1045,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1077,10 +1068,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1100,10 +1091,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1117,16 +1108,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1140,16 +1131,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1163,22 +1154,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920240</v>
+        <v>21330051920036</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1186,16 +1177,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1209,47 +1200,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920037</v>
+        <v>20330051920018</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -796,16 +796,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,16 +822,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +977,7 @@
         <v>90.63</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -106,12 +100,6 @@
     <t>LAGUNES</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -128,12 +116,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
@@ -601,19 +583,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>89.47</v>
+        <v>92.11</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -770,19 +752,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -939,19 +921,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1013,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1051,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1068,22 +1050,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920086</v>
+        <v>21330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1091,22 +1073,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920105</v>
+        <v>21330051920240</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1114,22 +1096,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920235</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1137,22 +1119,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920240</v>
+        <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1160,70 +1142,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920036</v>
+        <v>20330051920018</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920037</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920018</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -94,7 +97,7 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>NAZARIO</t>
   </si>
   <si>
     <t>LAGUNES</t>
@@ -112,7 +115,7 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>NAZARIO</t>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -128,9 +131,6 @@
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920077</v>
+        <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1042,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920235</v>
+        <v>21330051920077</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1062,10 +1062,10 @@
         <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920240</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1108,10 +1108,10 @@
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920018</v>
+        <v>21330051920037</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1157,10 +1157,10 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,58 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
   </si>
 </sst>
 </file>
@@ -872,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>87.18000000000001</v>
+        <v>97.44</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -898,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -924,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -950,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -976,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,22 +991,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1050,16 +1014,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920077</v>
+        <v>21330051920092</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1068,99 +1032,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920235</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920240</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920036</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920037</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
